--- a/Sajjad data/by_country_and_state/USA/TN.xlsx
+++ b/Sajjad data/by_country_and_state/USA/TN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="496">
   <si>
     <t>Business Name</t>
   </si>
@@ -1328,6 +1328,177 @@
   </si>
   <si>
     <t>2026-10-24T23:05:36.903Z</t>
+  </si>
+  <si>
+    <t>Dr. Kevin K. Dillard, DDS</t>
+  </si>
+  <si>
+    <t>(615) 896-7002</t>
+  </si>
+  <si>
+    <t>1814 Memorial Blvd, Murfreesboro, TN 37129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kevin+K.+Dillard,+DDS/data=!4m7!3m6!1s0x8864078844be1831:0xdc3b2087efc23bb!8m2!3d35.8728731!4d-86.3849551!16s%2Fg%2F1tdksjmk!19sChIJMRi-RIgHZIgRuyP8fgiyww0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:10.602Z</t>
+  </si>
+  <si>
+    <t>Dr. George W. Morton, DDS</t>
+  </si>
+  <si>
+    <t>(615) 895-3888</t>
+  </si>
+  <si>
+    <t>604 E Clark Blvd, Murfreesboro, TN 37130</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+George+W.+Morton,+DDS/data=!4m7!3m6!1s0x8863f87ffbf723d9:0x23ea4a7fe0409d55!8m2!3d35.8604129!4d-86.3785885!16s%2Fg%2F1tdc5z3z!19sChIJ2SP3-3_4Y4gRVZ1A4H9K6iM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:12.966Z</t>
+  </si>
+  <si>
+    <t>Dr. Gregory Nicholson</t>
+  </si>
+  <si>
+    <t>(615) 893-5500</t>
+  </si>
+  <si>
+    <t>1819 Lascassas Pike, Murfreesboro, TN 37130</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gregory+Nicholson/data=!4m7!3m6!1s0x88640766b29e18a1:0xc5832538c6318977!8m2!3d35.8658753!4d-86.3623848!16s%2Fg%2F11sb936h89!19sChIJoRiesmYHZIgRd4kxxjglg8U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:38.907Z</t>
+  </si>
+  <si>
+    <t>Dr. Jack Mallette &amp; Dr. Joseph Faiz</t>
+  </si>
+  <si>
+    <t>(615) 494-5437</t>
+  </si>
+  <si>
+    <t>2910 Old Fort Pkwy, Murfreesboro, TN 37128</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jack+Mallette+%26+Dr.+Joseph+Faiz/data=!4m7!3m6!1s0x8863f7bff8a2cf37:0x5f23f53bd5b01854!8m2!3d35.84552!4d-86.4494694!16s%2Fg%2F1vgqdtsx!19sChIJN8-i-L_3Y4gRVBiw1Tv1I18?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:09.858Z</t>
+  </si>
+  <si>
+    <t>Snodgrass David J DDS</t>
+  </si>
+  <si>
+    <t>(615) 225-0700</t>
+  </si>
+  <si>
+    <t>1747 Medical Center Pkwy #140, Murfreesboro, TN 37129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Snodgrass+David+J+DDS/data=!4m7!3m6!1s0x8863f7fe894715eb:0x5f36e10d2da42c5a!8m2!3d35.8572332!4d-86.4247979!16s%2Fg%2F1261rrx6z!19sChIJ6xVHif73Y4gRWiykLQ3hNl8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:13.102Z</t>
+  </si>
+  <si>
+    <t>Brushem</t>
+  </si>
+  <si>
+    <t>(615) 890-0454</t>
+  </si>
+  <si>
+    <t>132 Heritage Park Dr #0564, Murfreesboro, TN 37129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brushem/data=!4m7!3m6!1s0x8864079a8c8dbaef:0x775b2941389e8adf!8m2!3d35.8744171!4d-86.3872503!16s%2Fg%2F1262jg973!19sChIJ77qNjJoHZIgR34qeOEEpW3c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:19.913Z</t>
+  </si>
+  <si>
+    <t>Gaither J Wade DDS</t>
+  </si>
+  <si>
+    <t>(615) 895-5888</t>
+  </si>
+  <si>
+    <t>301 Uptown Square, Murfreesboro, TN 37129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gaither+J+Wade+DDS/data=!4m7!3m6!1s0x8864079b8ff383cb:0x11149611c5c139ef!8m2!3d35.875655!4d-86.3846282!16s%2Fg%2F1tfln4x6!19sChIJy4Pzj5sHZIgR7znBxRGWFBE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:47.510Z</t>
+  </si>
+  <si>
+    <t>Dr. Fenton P. Hardison, DDS</t>
+  </si>
+  <si>
+    <t>(615) 893-7736</t>
+  </si>
+  <si>
+    <t>1725 Medical Center Pkwy #100, Murfreesboro, TN 37129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Fenton+P.+Hardison,+DDS/data=!4m7!3m6!1s0x8863f7fc1b766f69:0x767648ecec91e92e!8m2!3d35.8575773!4d-86.4241639!16s%2Fg%2F1tx8tymp!19sChIJaW92G_z3Y4gRLumR7OxIdnY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:50.027Z</t>
+  </si>
+  <si>
+    <t>Ross Fahey</t>
+  </si>
+  <si>
+    <t>(615) 890-8000</t>
+  </si>
+  <si>
+    <t>2565 Rideout Ln, Murfreesboro, TN 37128</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ross+Fahey/data=!4m7!3m6!1s0x8863f7c01be0a8ad:0xd6f89ba9c3e83c85!8m2!3d35.8418199!4d-86.439372!16s%2Fg%2F11qgb7lcg1!19sChIJrajgG8D3Y4gRhTzow6mb-NY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:52.456Z</t>
+  </si>
+  <si>
+    <t>Middle Tennessee Medical Center: Ferguson Gordon DDS</t>
+  </si>
+  <si>
+    <t>(615) 396-4100</t>
+  </si>
+  <si>
+    <t>1700 Medical Center Pkwy, Murfreesboro, TN 37129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Middle+Tennessee+Medical+Center:+Ferguson+Gordon+DDS/data=!4m7!3m6!1s0x8863f8013fc1759f:0x81433ed6fa76d9a7!8m2!3d35.8607437!4d-86.4243423!16s%2Fg%2F1hc1hbqt2!19sChIJn3XBPwH4Y4gRp9l2-tY-Q4E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:33:09.704Z</t>
+  </si>
+  <si>
+    <t>Dr. Steven Daniel</t>
+  </si>
+  <si>
+    <t>(615) 890-7186</t>
+  </si>
+  <si>
+    <t>1255 N Highland Ave A, Murfreesboro, TN 37130</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–12 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Steven+Daniel/data=!4m7!3m6!1s0x8863f87f3c26a927:0x2cc10c2bf1342047!8m2!3d35.8592061!4d-86.3822349!16s%2Fg%2F11kjq669jp!19sChIJJ6kmPH_4Y4gRRyA08SsMwSw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:13.712Z</t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4759,6 +4930,457 @@
         <v>438</v>
       </c>
     </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>439</v>
+      </c>
+      <c r="B75" t="s">
+        <v>440</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>441</v>
+      </c>
+      <c r="E75" t="s">
+        <v>435</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>117</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>442</v>
+      </c>
+      <c r="M75" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>444</v>
+      </c>
+      <c r="B76" t="s">
+        <v>445</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>446</v>
+      </c>
+      <c r="E76" t="s">
+        <v>435</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>392</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>22</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>447</v>
+      </c>
+      <c r="M76" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>449</v>
+      </c>
+      <c r="B77" t="s">
+        <v>450</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" t="s">
+        <v>435</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>29</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>42</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>452</v>
+      </c>
+      <c r="M77" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>454</v>
+      </c>
+      <c r="B78" t="s">
+        <v>455</v>
+      </c>
+      <c r="C78" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" t="s">
+        <v>456</v>
+      </c>
+      <c r="E78" t="s">
+        <v>435</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>29</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>22</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>457</v>
+      </c>
+      <c r="M78" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>459</v>
+      </c>
+      <c r="B79" t="s">
+        <v>460</v>
+      </c>
+      <c r="C79" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" t="s">
+        <v>461</v>
+      </c>
+      <c r="E79" t="s">
+        <v>435</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>137</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>22</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>462</v>
+      </c>
+      <c r="M79" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>464</v>
+      </c>
+      <c r="B80" t="s">
+        <v>465</v>
+      </c>
+      <c r="C80" t="s">
+        <v>222</v>
+      </c>
+      <c r="D80" t="s">
+        <v>466</v>
+      </c>
+      <c r="E80" t="s">
+        <v>435</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" t="s">
+        <v>59</v>
+      </c>
+      <c r="J80" t="s">
+        <v>42</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>467</v>
+      </c>
+      <c r="M80" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>469</v>
+      </c>
+      <c r="B81" t="s">
+        <v>470</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>471</v>
+      </c>
+      <c r="E81" t="s">
+        <v>435</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>42</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>472</v>
+      </c>
+      <c r="M81" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>474</v>
+      </c>
+      <c r="B82" t="s">
+        <v>475</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" t="s">
+        <v>476</v>
+      </c>
+      <c r="E82" t="s">
+        <v>435</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>123</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s">
+        <v>42</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>477</v>
+      </c>
+      <c r="M82" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>479</v>
+      </c>
+      <c r="B83" t="s">
+        <v>480</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" t="s">
+        <v>481</v>
+      </c>
+      <c r="E83" t="s">
+        <v>435</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>29</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>42</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>482</v>
+      </c>
+      <c r="M83" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>484</v>
+      </c>
+      <c r="B84" t="s">
+        <v>485</v>
+      </c>
+      <c r="C84" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" t="s">
+        <v>486</v>
+      </c>
+      <c r="E84" t="s">
+        <v>435</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" t="s">
+        <v>59</v>
+      </c>
+      <c r="J84" t="s">
+        <v>42</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>487</v>
+      </c>
+      <c r="M84" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>489</v>
+      </c>
+      <c r="B85" t="s">
+        <v>490</v>
+      </c>
+      <c r="C85" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" t="s">
+        <v>491</v>
+      </c>
+      <c r="E85" t="s">
+        <v>435</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85" t="s">
+        <v>492</v>
+      </c>
+      <c r="J85" t="s">
+        <v>493</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>494</v>
+      </c>
+      <c r="M85" t="s">
+        <v>495</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
